--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2015/WEST_VIRGINIA_2015.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2015/WEST_VIRGINIA_2015.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D212"/>
+  <dimension ref="A1:D206"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Chamula</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Frontera Comalapa</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Huehuetán</t>
@@ -465,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -478,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -491,9 +521,14 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mazapa de Madero</t>
+          <t>Mazapa De Madero</t>
         </is>
       </c>
       <c r="C10">
@@ -504,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Ocosingo</t>
@@ -517,9 +557,14 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>San Cristóbal de las Casas</t>
+          <t>San Cristóbal De Las Casas</t>
         </is>
       </c>
       <c r="C12">
@@ -530,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -543,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Tecpatán</t>
@@ -556,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Total</t>
@@ -576,7 +636,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C16">
@@ -587,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -600,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -631,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Saltillo</t>
@@ -644,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Total</t>
@@ -659,7 +739,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -675,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -688,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -701,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -714,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -727,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -740,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -753,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -766,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Total</t>
@@ -797,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -810,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Total</t>
@@ -825,13 +955,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estado de México_x000D_
-</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Coacalco de Berriozábal</t>
+          <t>Coacalco De Berriozábal</t>
         </is>
       </c>
       <c r="C34">
@@ -842,9 +971,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C35">
@@ -855,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Jocotitlán</t>
@@ -868,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -881,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Polotitlán</t>
@@ -894,9 +1043,14 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C39">
@@ -907,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -920,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Temascalcingo</t>
@@ -933,9 +1097,14 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C42">
@@ -946,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Tlatlaya</t>
@@ -959,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Zacualpan</t>
@@ -972,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1003,9 +1187,14 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Apaseo el Alto</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C47">
@@ -1016,9 +1205,14 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna de la Independencia Nacional</t>
+          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
         </is>
       </c>
       <c r="C48">
@@ -1029,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Huanímaro</t>
@@ -1042,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Jerécuaro</t>
@@ -1055,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>León</t>
@@ -1068,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Manuel Doblado</t>
@@ -1081,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -1094,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Romita</t>
@@ -1107,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -1120,9 +1349,14 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Silao de la Victoria</t>
+          <t>Silao De La Victoria</t>
         </is>
       </c>
       <c r="C56">
@@ -1133,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1153,7 +1392,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C58">
@@ -1164,9 +1403,14 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ajuchitlán del Progreso</t>
+          <t>Ajuchitlán Del Progreso</t>
         </is>
       </c>
       <c r="C59">
@@ -1177,9 +1421,14 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ayutla de los Libres</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C60">
@@ -1190,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Azoyú</t>
@@ -1203,9 +1457,14 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cutzamala de Pinzón</t>
+          <t>Cutzamala De Pinzón</t>
         </is>
       </c>
       <c r="C62">
@@ -1216,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Malinaltepec</t>
@@ -1229,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Petatlán</t>
@@ -1242,9 +1511,14 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C65">
@@ -1255,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1286,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Calnali</t>
@@ -1299,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Eloxochitlán</t>
@@ -1312,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Huichapan</t>
@@ -1325,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -1338,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Metepec</t>
@@ -1351,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Metztitlán</t>
@@ -1364,9 +1673,14 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Santiago de Anaya</t>
+          <t>Santiago De Anaya</t>
         </is>
       </c>
       <c r="C74">
@@ -1377,9 +1691,14 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tenango de Doria</t>
+          <t>Tenango De Doria</t>
         </is>
       </c>
       <c r="C75">
@@ -1390,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Tepeapulco</t>
@@ -1403,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1423,7 +1752,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ahualulco de Mercado</t>
+          <t>Ahualulco De Mercado</t>
         </is>
       </c>
       <c r="C78">
@@ -1434,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Casimiro Castillo</t>
@@ -1447,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Degollado</t>
@@ -1460,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1473,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -1486,9 +1835,14 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ojuelos de Jalisco</t>
+          <t>Ojuelos De Jalisco</t>
         </is>
       </c>
       <c r="C83">
@@ -1499,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Puerto Vallarta</t>
@@ -1512,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Quitupan</t>
@@ -1525,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -1538,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>San Pedro Tlaquepaque</t>
@@ -1551,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -1564,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -1577,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1608,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Irimbo</t>
@@ -1621,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -1634,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -1647,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Paracho</t>
@@ -1660,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Purépero</t>
@@ -1673,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Santa Ana Maya</t>
@@ -1686,9 +2105,14 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tiquicheo de Nicolás Romero</t>
+          <t>Tiquicheo De Nicolás Romero</t>
         </is>
       </c>
       <c r="C98">
@@ -1699,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -1712,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -1725,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -1738,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1769,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Cuautla</t>
@@ -1782,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -1795,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Miacatlán</t>
@@ -1808,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Tlaquiltenango</t>
@@ -1821,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1852,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Ruíz</t>
@@ -1865,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1885,7 +2364,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Mier y Noriega</t>
+          <t>Mier Y Noriega</t>
         </is>
       </c>
       <c r="C112">
@@ -1896,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Monterrey</t>
@@ -1909,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Santiago</t>
@@ -1922,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1942,7 +2436,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Acatlán de Pérez Figueroa</t>
+          <t>Acatlán De Pérez Figueroa</t>
         </is>
       </c>
       <c r="C116">
@@ -1953,9 +2447,14 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C117">
@@ -1966,9 +2465,14 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Putla Villa de Guerrero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C118">
@@ -1979,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>San Andrés Paxtlán</t>
@@ -1992,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>San Andrés Yaá</t>
@@ -2005,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>San Juan Bautista Valle Nacional</t>
@@ -2018,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>San Juan Cacahuatepec</t>
@@ -2031,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>San Juan Lalana</t>
@@ -2044,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>San Juan Teita</t>
@@ -2057,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>San Juan Teposcolula</t>
@@ -2070,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>San Mateo Peñasco</t>
@@ -2083,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>San Miguel Soyaltepec</t>
@@ -2096,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>San Sebastián Abasolo</t>
@@ -2109,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Santa Catarina Juquila</t>
@@ -2122,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Santa María Chilchotla</t>
@@ -2135,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Santa María Yolotepec</t>
@@ -2148,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Santa María Zacatepec</t>
@@ -2161,6 +2735,11 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>Santiago Matatlán</t>
@@ -2174,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Santiago Yosondúa</t>
@@ -2187,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2218,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Chietla</t>
@@ -2231,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Chila</t>
@@ -2244,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Honey</t>
@@ -2257,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Huejotzingo</t>
@@ -2270,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Hueytamalco</t>
@@ -2283,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>San Pedro Cholula</t>
@@ -2296,9 +2915,14 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>San Salvador el Verde</t>
+          <t>San Salvador El Verde</t>
         </is>
       </c>
       <c r="C143">
@@ -2309,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -2322,9 +2951,14 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Tlacotepec de Benito Juárez</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C145">
@@ -2335,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2355,7 +2994,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Landa de Matamoros</t>
+          <t>Landa De Matamoros</t>
         </is>
       </c>
       <c r="C147">
@@ -2366,9 +3005,14 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Pinal de Amoles</t>
+          <t>Pinal De Amoles</t>
         </is>
       </c>
       <c r="C148">
@@ -2379,9 +3023,14 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C149">
@@ -2392,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Tolimán</t>
@@ -2405,6 +3059,11 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2436,6 +3095,11 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2467,6 +3131,11 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>Ciudad Fernández</t>
@@ -2480,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Matlapa</t>
@@ -2493,9 +3167,14 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>San Ciro de Acosta</t>
+          <t>San Ciro De Acosta</t>
         </is>
       </c>
       <c r="C157">
@@ -2506,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2537,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Mazatlán</t>
@@ -2550,6 +3239,11 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>Navolato</t>
@@ -2563,6 +3257,11 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2594,6 +3293,11 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2625,6 +3329,11 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2656,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Mainero</t>
@@ -2669,6 +3383,11 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -2682,9 +3401,14 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Soto la Marina</t>
+          <t>Soto La Marina</t>
         </is>
       </c>
       <c r="C170">
@@ -2695,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2726,6 +3455,11 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2757,6 +3491,11 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>Atoyac</t>
@@ -2770,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Atzalan</t>
@@ -2783,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Calcahualco</t>
@@ -2796,6 +3545,11 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>Coatepec</t>
@@ -2809,6 +3563,11 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>Comapa</t>
@@ -2822,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -2835,6 +3599,11 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>Hidalgotitlán</t>
@@ -2848,6 +3617,11 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>Huatusco</t>
@@ -2861,9 +3635,14 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Hueyapan de Ocampo</t>
+          <t>Hueyapan De Ocampo</t>
         </is>
       </c>
       <c r="C183">
@@ -2874,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>Jesús Carranza</t>
@@ -2887,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>Las Choapas</t>
@@ -2900,9 +3689,14 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C186">
@@ -2913,6 +3707,11 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>Orizaba</t>
@@ -2926,6 +3725,11 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -2939,6 +3743,11 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -2952,6 +3761,11 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>Tezonapa</t>
@@ -2965,6 +3779,11 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -2978,6 +3797,11 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>Tihuatlán</t>
@@ -2991,6 +3815,11 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
           <t>Tlachichilco</t>
@@ -3004,6 +3833,11 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>Tlapacoyan</t>
@@ -3017,6 +3851,11 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>Zongolica</t>
@@ -3030,9 +3869,14 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Zozocolco de Hidalgo</t>
+          <t>Zozocolco De Hidalgo</t>
         </is>
       </c>
       <c r="C196">
@@ -3043,6 +3887,11 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3074,6 +3923,11 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>Sucilá</t>
@@ -3087,6 +3941,11 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3118,6 +3977,11 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>Miguel Auza</t>
@@ -3131,6 +3995,11 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>Pinos</t>
@@ -3144,6 +4013,11 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>Valparaíso</t>
@@ -3157,6 +4031,11 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3180,41 +4059,6 @@
       </c>
       <c r="D206">
         <v>1</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
